--- a/ET-release8.1/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/MonsterGroupConfig.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="MonsterGroupProto" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525" concurrentCalc="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
   <si>
     <t>Id</t>
   </si>
@@ -34,15 +34,27 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>0,0,0</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>范围/1000</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>Range</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>地图id</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>mapId</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8800,0,-3420</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-8000,0,9433</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -107,13 +119,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -415,7 +430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C3:E7"/>
+  <dimension ref="C3:F7"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
@@ -424,7 +439,7 @@
     <col min="6" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
@@ -432,10 +447,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
@@ -443,10 +461,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
@@ -456,27 +477,36 @@
       <c r="E5" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="F5" s="3" t="s">
+        <v>1</v>
+      </c>
     </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>3001</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>5</v>
+      <c r="D6" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="E6" s="1">
-        <v>5000</v>
+        <v>1000</v>
+      </c>
+      <c r="F6" s="1">
+        <v>10002</v>
       </c>
     </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:6" x14ac:dyDescent="0.3">
       <c r="C7" s="1">
         <v>3002</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>5</v>
+      <c r="D7" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="E7" s="1">
-        <v>5000</v>
+        <v>1000</v>
+      </c>
+      <c r="F7" s="1">
+        <v>10002</v>
       </c>
     </row>
   </sheetData>
